--- a/TaaS COE Mandays Catalog.xlsx
+++ b/TaaS COE Mandays Catalog.xlsx
@@ -5,19 +5,20 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tm365-my.sharepoint.com/personal/aminah_izazi_tm_com_my1/Documents/Documents/VS Code/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tm365-my.sharepoint.com/personal/aminah_izazi_tm_com_my1/Documents/Documents/Mandays Calculator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1444" documentId="14_{EA5759CD-77BE-4769-9996-D07B3A23EF31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D54FBF38-71B5-4AB4-B0FE-AE6F5655D4A3}"/>
+  <xr:revisionPtr revIDLastSave="1460" documentId="14_{EA5759CD-77BE-4769-9996-D07B3A23EF31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BDF5D7E8-4888-4D8F-956D-7D4A66388A16}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="4" xr2:uid="{63D26A3C-1657-43F1-8D86-23BA2E534788}"/>
+    <workbookView minimized="1" xWindow="1536" yWindow="1536" windowWidth="17280" windowHeight="8964" activeTab="4" xr2:uid="{63D26A3C-1657-43F1-8D86-23BA2E534788}"/>
   </bookViews>
   <sheets>
-    <sheet name="COLC" sheetId="7" r:id="rId1"/>
-    <sheet name="CIC (New)" sheetId="9" r:id="rId2"/>
-    <sheet name="CSC(New)" sheetId="6" r:id="rId3"/>
-    <sheet name="CPC (New)" sheetId="4" r:id="rId4"/>
-    <sheet name="JNC (New)" sheetId="5" r:id="rId5"/>
+    <sheet name="CIC (New)" sheetId="9" r:id="rId1"/>
+    <sheet name="CSC(New)" sheetId="6" r:id="rId2"/>
+    <sheet name="CPC (New)" sheetId="4" r:id="rId3"/>
+    <sheet name="JNC (New)" sheetId="5" r:id="rId4"/>
+    <sheet name="CLP" sheetId="10" r:id="rId5"/>
+    <sheet name="eShop" sheetId="11" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="196">
   <si>
     <t>Item</t>
   </si>
@@ -602,13 +603,52 @@
   </si>
   <si>
     <t>Offer Group Tag</t>
+  </si>
+  <si>
+    <t>Add/Update/Remove Icon</t>
+  </si>
+  <si>
+    <t>Add/Update/Remove Image</t>
+  </si>
+  <si>
+    <t>Add/Update/Remove URL</t>
+  </si>
+  <si>
+    <t>Add/Update/Remove Banner</t>
+  </si>
+  <si>
+    <t>Add/Update/Remove Change copytext</t>
+  </si>
+  <si>
+    <t>Add/Update/Disable offer/product</t>
+  </si>
+  <si>
+    <t>Add/Update/Remove campaign visuals</t>
+  </si>
+  <si>
+    <t>Add/Update/Remove Tag</t>
+  </si>
+  <si>
+    <t>Add/Update/Remove Catalog</t>
+  </si>
+  <si>
+    <t>Add/Update/Remove Channel</t>
+  </si>
+  <si>
+    <t>Update whitelist field</t>
+  </si>
+  <si>
+    <t>Config Benefit Group</t>
+  </si>
+  <si>
+    <t>Update vascode into URL</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -667,8 +707,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -709,6 +755,12 @@
       <patternFill patternType="solid">
         <fgColor theme="5"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF94DCF8"/>
+        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
   </fills>
@@ -883,7 +935,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -945,22 +997,7 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -981,36 +1018,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1021,6 +1028,70 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1037,10 +1108,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1359,30 +1426,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C17C7C91-7D27-4EC2-A37A-B6B9C6BE3F0D}">
-  <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="17" t="s">
-        <v>3</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB9F45FD-B513-4178-9D7C-8964321ED9E5}">
   <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1444,7 +1487,7 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="29" t="s">
+      <c r="A3" s="43" t="s">
         <v>39</v>
       </c>
       <c r="B3" s="1">
@@ -1463,13 +1506,13 @@
       <c r="F3" t="s">
         <v>41</v>
       </c>
-      <c r="G3" s="33">
+      <c r="G3" s="44">
         <f>SUM(D3:D7)</f>
         <v>0.1</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="29"/>
+      <c r="A4" s="43"/>
       <c r="B4" s="1">
         <v>1</v>
       </c>
@@ -1486,10 +1529,10 @@
       <c r="F4" t="s">
         <v>43</v>
       </c>
-      <c r="G4" s="34"/>
+      <c r="G4" s="45"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="29"/>
+      <c r="A5" s="43"/>
       <c r="B5" s="1">
         <v>1</v>
       </c>
@@ -1506,10 +1549,10 @@
       <c r="F5" t="s">
         <v>45</v>
       </c>
-      <c r="G5" s="34"/>
+      <c r="G5" s="45"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="29"/>
+      <c r="A6" s="43"/>
       <c r="B6" s="1">
         <v>1</v>
       </c>
@@ -1526,10 +1569,10 @@
       <c r="F6" t="s">
         <v>47</v>
       </c>
-      <c r="G6" s="34"/>
+      <c r="G6" s="45"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="29"/>
+      <c r="A7" s="43"/>
       <c r="B7" s="1">
         <v>1</v>
       </c>
@@ -1546,7 +1589,7 @@
       <c r="F7" t="s">
         <v>49</v>
       </c>
-      <c r="G7" s="34"/>
+      <c r="G7" s="45"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
@@ -1568,7 +1611,7 @@
       <c r="F8" t="s">
         <v>51</v>
       </c>
-      <c r="G8" s="32">
+      <c r="G8" s="29">
         <f>SUM(D8)</f>
         <v>0.01</v>
       </c>
@@ -1585,7 +1628,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CADF697-8BA9-4F97-8B1E-2355AB484243}">
   <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1622,7 +1665,7 @@
       </c>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="47" t="s">
         <v>52</v>
       </c>
       <c r="B2" s="1">
@@ -1635,19 +1678,19 @@
         <f>ROUNDUP(C2/480,2)</f>
         <v>0.02</v>
       </c>
-      <c r="E2" s="30" t="s">
+      <c r="E2" s="46" t="s">
         <v>53</v>
       </c>
       <c r="F2" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="G2" s="33">
+      <c r="G2" s="44">
         <f>SUM(D2:D4)</f>
         <v>6.9999999999999993E-2</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="31"/>
+      <c r="A3" s="47"/>
       <c r="B3" s="1">
         <v>1</v>
       </c>
@@ -1658,14 +1701,14 @@
         <f t="shared" ref="D3:D10" si="0">ROUNDUP(C3/480,2)</f>
         <v>0.04</v>
       </c>
-      <c r="E3" s="30"/>
+      <c r="E3" s="46"/>
       <c r="F3" t="s">
         <v>55</v>
       </c>
-      <c r="G3" s="33"/>
+      <c r="G3" s="44"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="31"/>
+      <c r="A4" s="47"/>
       <c r="B4" s="1">
         <v>1</v>
       </c>
@@ -1676,14 +1719,14 @@
         <f t="shared" si="0"/>
         <v>0.01</v>
       </c>
-      <c r="E4" s="30"/>
+      <c r="E4" s="46"/>
       <c r="F4" t="s">
         <v>56</v>
       </c>
-      <c r="G4" s="33"/>
+      <c r="G4" s="44"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="31" t="s">
+      <c r="A5" s="47" t="s">
         <v>57</v>
       </c>
       <c r="B5">
@@ -1696,19 +1739,19 @@
         <f t="shared" si="0"/>
         <v>0.01</v>
       </c>
-      <c r="E5" s="30" t="s">
+      <c r="E5" s="46" t="s">
         <v>58</v>
       </c>
       <c r="F5" t="s">
         <v>59</v>
       </c>
-      <c r="G5" s="33">
+      <c r="G5" s="44">
         <f>SUM(D5:D6)</f>
         <v>0.02</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="31"/>
+      <c r="A6" s="47"/>
       <c r="B6">
         <v>1</v>
       </c>
@@ -1719,11 +1762,11 @@
         <f t="shared" si="0"/>
         <v>0.01</v>
       </c>
-      <c r="E6" s="30"/>
+      <c r="E6" s="46"/>
       <c r="F6" t="s">
         <v>60</v>
       </c>
-      <c r="G6" s="34"/>
+      <c r="G6" s="45"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
@@ -1834,7 +1877,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CAAB2C6-DFD1-4C08-8D00-BE58AEE3ED22}">
   <dimension ref="A1:G81"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1849,46 +1892,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="37" t="s">
+      <c r="B1" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="D1" s="37" t="s">
+      <c r="D1" s="32" t="s">
         <v>169</v>
       </c>
-      <c r="E1" s="37" t="s">
+      <c r="E1" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="F1" s="37" t="s">
+      <c r="F1" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="37" t="s">
+      <c r="G1" s="32" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="38">
-        <v>1</v>
-      </c>
-      <c r="C2" s="38">
+      <c r="B2" s="33">
+        <v>1</v>
+      </c>
+      <c r="C2" s="33">
         <v>20</v>
       </c>
-      <c r="D2" s="38">
+      <c r="D2" s="33">
         <f t="shared" ref="D2:D33" si="0">ROUND(C2/480,3)</f>
         <v>4.2000000000000003E-2</v>
       </c>
-      <c r="E2" s="38" t="s">
+      <c r="E2" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="38" t="s">
+      <c r="F2" s="33" t="s">
         <v>5</v>
       </c>
       <c r="G2" s="5">
@@ -1897,23 +1940,23 @@
       </c>
     </row>
     <row r="3" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A3" s="44" t="s">
+      <c r="A3" s="53" t="s">
         <v>72</v>
       </c>
-      <c r="B3" s="47">
-        <v>1</v>
-      </c>
-      <c r="C3" s="39">
-        <v>1</v>
-      </c>
-      <c r="D3" s="39">
+      <c r="B3" s="51">
+        <v>1</v>
+      </c>
+      <c r="C3" s="34">
+        <v>1</v>
+      </c>
+      <c r="D3" s="34">
         <f t="shared" si="0"/>
         <v>2E-3</v>
       </c>
-      <c r="E3" s="40" t="s">
+      <c r="E3" s="35" t="s">
         <v>73</v>
       </c>
-      <c r="F3" s="41" t="s">
+      <c r="F3" s="36" t="s">
         <v>74</v>
       </c>
       <c r="G3" s="5">
@@ -1922,239 +1965,239 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="45"/>
-      <c r="B4" s="48"/>
-      <c r="C4" s="39">
+      <c r="A4" s="54"/>
+      <c r="B4" s="56"/>
+      <c r="C4" s="34">
         <v>5</v>
       </c>
-      <c r="D4" s="39">
+      <c r="D4" s="34">
         <f t="shared" si="0"/>
         <v>0.01</v>
       </c>
-      <c r="E4" s="41" t="s">
+      <c r="E4" s="36" t="s">
         <v>75</v>
       </c>
-      <c r="F4" s="41" t="s">
+      <c r="F4" s="36" t="s">
         <v>76</v>
       </c>
       <c r="G4" s="5"/>
     </row>
     <row r="5" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="45"/>
-      <c r="B5" s="48"/>
-      <c r="C5" s="39">
+      <c r="A5" s="54"/>
+      <c r="B5" s="56"/>
+      <c r="C5" s="34">
         <v>10</v>
       </c>
-      <c r="D5" s="39">
+      <c r="D5" s="34">
         <f t="shared" si="0"/>
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="E5" s="41" t="s">
+      <c r="E5" s="36" t="s">
         <v>77</v>
       </c>
-      <c r="F5" s="41" t="s">
+      <c r="F5" s="36" t="s">
         <v>78</v>
       </c>
       <c r="G5" s="5"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="45"/>
-      <c r="B6" s="48"/>
-      <c r="C6" s="39">
+      <c r="A6" s="54"/>
+      <c r="B6" s="56"/>
+      <c r="C6" s="34">
         <v>30</v>
       </c>
-      <c r="D6" s="39">
+      <c r="D6" s="34">
         <f t="shared" si="0"/>
         <v>6.3E-2</v>
       </c>
-      <c r="E6" s="41" t="s">
+      <c r="E6" s="36" t="s">
         <v>79</v>
       </c>
-      <c r="F6" s="41" t="s">
+      <c r="F6" s="36" t="s">
         <v>80</v>
       </c>
       <c r="G6" s="5"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="45"/>
-      <c r="B7" s="48"/>
-      <c r="C7" s="39">
-        <v>1</v>
-      </c>
-      <c r="D7" s="39">
+      <c r="A7" s="54"/>
+      <c r="B7" s="56"/>
+      <c r="C7" s="34">
+        <v>1</v>
+      </c>
+      <c r="D7" s="34">
         <f t="shared" si="0"/>
         <v>2E-3</v>
       </c>
-      <c r="E7" s="41" t="s">
+      <c r="E7" s="36" t="s">
         <v>81</v>
       </c>
-      <c r="F7" s="41" t="s">
+      <c r="F7" s="36" t="s">
         <v>82</v>
       </c>
       <c r="G7" s="5"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="45"/>
-      <c r="B8" s="48"/>
-      <c r="C8" s="39">
+      <c r="A8" s="54"/>
+      <c r="B8" s="56"/>
+      <c r="C8" s="34">
         <v>60</v>
       </c>
-      <c r="D8" s="39">
+      <c r="D8" s="34">
         <f t="shared" si="0"/>
         <v>0.125</v>
       </c>
-      <c r="E8" s="41" t="s">
+      <c r="E8" s="36" t="s">
         <v>83</v>
       </c>
-      <c r="F8" s="41" t="s">
+      <c r="F8" s="36" t="s">
         <v>84</v>
       </c>
       <c r="G8" s="5"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="45"/>
-      <c r="B9" s="48"/>
-      <c r="C9" s="39">
+      <c r="A9" s="54"/>
+      <c r="B9" s="56"/>
+      <c r="C9" s="34">
         <v>5</v>
       </c>
-      <c r="D9" s="39">
+      <c r="D9" s="34">
         <f t="shared" si="0"/>
         <v>0.01</v>
       </c>
-      <c r="E9" s="41" t="s">
+      <c r="E9" s="36" t="s">
         <v>85</v>
       </c>
-      <c r="F9" s="41" t="s">
+      <c r="F9" s="36" t="s">
         <v>86</v>
       </c>
       <c r="G9" s="5"/>
     </row>
     <row r="10" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A10" s="45"/>
-      <c r="B10" s="48"/>
-      <c r="C10" s="39">
-        <v>1</v>
-      </c>
-      <c r="D10" s="39">
+      <c r="A10" s="54"/>
+      <c r="B10" s="56"/>
+      <c r="C10" s="34">
+        <v>1</v>
+      </c>
+      <c r="D10" s="34">
         <f t="shared" si="0"/>
         <v>2E-3</v>
       </c>
-      <c r="E10" s="41" t="s">
+      <c r="E10" s="36" t="s">
         <v>87</v>
       </c>
-      <c r="F10" s="41" t="s">
+      <c r="F10" s="36" t="s">
         <v>88</v>
       </c>
       <c r="G10" s="5"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="45"/>
-      <c r="B11" s="48"/>
-      <c r="C11" s="39">
-        <v>1</v>
-      </c>
-      <c r="D11" s="39">
+      <c r="A11" s="54"/>
+      <c r="B11" s="56"/>
+      <c r="C11" s="34">
+        <v>1</v>
+      </c>
+      <c r="D11" s="34">
         <f t="shared" si="0"/>
         <v>2E-3</v>
       </c>
-      <c r="E11" s="41" t="s">
+      <c r="E11" s="36" t="s">
         <v>89</v>
       </c>
-      <c r="F11" s="41" t="s">
+      <c r="F11" s="36" t="s">
         <v>90</v>
       </c>
       <c r="G11" s="5"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="45"/>
-      <c r="B12" s="48"/>
-      <c r="C12" s="39">
+      <c r="A12" s="54"/>
+      <c r="B12" s="56"/>
+      <c r="C12" s="34">
         <v>2</v>
       </c>
-      <c r="D12" s="39">
+      <c r="D12" s="34">
         <f t="shared" si="0"/>
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="E12" s="41" t="s">
+      <c r="E12" s="36" t="s">
         <v>91</v>
       </c>
-      <c r="F12" s="41" t="s">
+      <c r="F12" s="36" t="s">
         <v>92</v>
       </c>
       <c r="G12" s="5"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="45"/>
-      <c r="B13" s="48"/>
-      <c r="C13" s="39">
+      <c r="A13" s="54"/>
+      <c r="B13" s="56"/>
+      <c r="C13" s="34">
         <v>5</v>
       </c>
-      <c r="D13" s="39">
+      <c r="D13" s="34">
         <f t="shared" si="0"/>
         <v>0.01</v>
       </c>
-      <c r="E13" s="41" t="s">
+      <c r="E13" s="36" t="s">
         <v>93</v>
       </c>
-      <c r="F13" s="41" t="s">
+      <c r="F13" s="36" t="s">
         <v>94</v>
       </c>
       <c r="G13" s="5"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="45"/>
-      <c r="B14" s="48"/>
-      <c r="C14" s="39">
-        <v>1</v>
-      </c>
-      <c r="D14" s="39">
+      <c r="A14" s="54"/>
+      <c r="B14" s="56"/>
+      <c r="C14" s="34">
+        <v>1</v>
+      </c>
+      <c r="D14" s="34">
         <f t="shared" si="0"/>
         <v>2E-3</v>
       </c>
-      <c r="E14" s="41" t="s">
+      <c r="E14" s="36" t="s">
         <v>95</v>
       </c>
-      <c r="F14" s="41" t="s">
+      <c r="F14" s="36" t="s">
         <v>96</v>
       </c>
       <c r="G14" s="5"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="46"/>
-      <c r="B15" s="49"/>
-      <c r="C15" s="39">
-        <v>1</v>
-      </c>
-      <c r="D15" s="39">
+      <c r="A15" s="55"/>
+      <c r="B15" s="52"/>
+      <c r="C15" s="34">
+        <v>1</v>
+      </c>
+      <c r="D15" s="34">
         <f t="shared" si="0"/>
         <v>2E-3</v>
       </c>
-      <c r="E15" s="41" t="s">
+      <c r="E15" s="36" t="s">
         <v>97</v>
       </c>
-      <c r="F15" s="41" t="s">
+      <c r="F15" s="36" t="s">
         <v>98</v>
       </c>
       <c r="G15" s="5"/>
     </row>
     <row r="16" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A16" s="50" t="s">
+      <c r="A16" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="B16" s="50">
-        <v>1</v>
-      </c>
-      <c r="C16" s="38">
-        <v>1</v>
-      </c>
-      <c r="D16" s="38">
+      <c r="B16" s="48">
+        <v>1</v>
+      </c>
+      <c r="C16" s="33">
+        <v>1</v>
+      </c>
+      <c r="D16" s="33">
         <f t="shared" si="0"/>
         <v>2E-3</v>
       </c>
-      <c r="E16" s="42" t="s">
+      <c r="E16" s="37" t="s">
         <v>99</v>
       </c>
-      <c r="F16" s="42" t="s">
+      <c r="F16" s="37" t="s">
         <v>100</v>
       </c>
       <c r="G16" s="5">
@@ -2163,239 +2206,239 @@
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="51"/>
-      <c r="B17" s="51"/>
-      <c r="C17" s="38">
+      <c r="A17" s="49"/>
+      <c r="B17" s="49"/>
+      <c r="C17" s="33">
         <v>5</v>
       </c>
-      <c r="D17" s="38">
+      <c r="D17" s="33">
         <f t="shared" si="0"/>
         <v>0.01</v>
       </c>
-      <c r="E17" s="38" t="s">
+      <c r="E17" s="33" t="s">
         <v>101</v>
       </c>
-      <c r="F17" s="42" t="s">
+      <c r="F17" s="37" t="s">
         <v>102</v>
       </c>
       <c r="G17" s="5"/>
     </row>
     <row r="18" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A18" s="51"/>
-      <c r="B18" s="51"/>
-      <c r="C18" s="38">
+      <c r="A18" s="49"/>
+      <c r="B18" s="49"/>
+      <c r="C18" s="33">
         <v>30</v>
       </c>
-      <c r="D18" s="38">
+      <c r="D18" s="33">
         <f t="shared" si="0"/>
         <v>6.3E-2</v>
       </c>
-      <c r="E18" s="38" t="s">
+      <c r="E18" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="F18" s="42" t="s">
+      <c r="F18" s="37" t="s">
         <v>103</v>
       </c>
       <c r="G18" s="5"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="51"/>
-      <c r="B19" s="51"/>
-      <c r="C19" s="38">
+      <c r="A19" s="49"/>
+      <c r="B19" s="49"/>
+      <c r="C19" s="33">
         <v>5</v>
       </c>
-      <c r="D19" s="38">
+      <c r="D19" s="33">
         <f t="shared" si="0"/>
         <v>0.01</v>
       </c>
-      <c r="E19" s="38" t="s">
+      <c r="E19" s="33" t="s">
         <v>85</v>
       </c>
-      <c r="F19" s="42" t="s">
+      <c r="F19" s="37" t="s">
         <v>86</v>
       </c>
       <c r="G19" s="5"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="51"/>
-      <c r="B20" s="51"/>
-      <c r="C20" s="38">
+      <c r="A20" s="49"/>
+      <c r="B20" s="49"/>
+      <c r="C20" s="33">
         <v>15</v>
       </c>
-      <c r="D20" s="38">
+      <c r="D20" s="33">
         <f t="shared" si="0"/>
         <v>3.1E-2</v>
       </c>
-      <c r="E20" s="38" t="s">
+      <c r="E20" s="33" t="s">
         <v>83</v>
       </c>
-      <c r="F20" s="42" t="s">
+      <c r="F20" s="37" t="s">
         <v>104</v>
       </c>
       <c r="G20" s="5"/>
     </row>
     <row r="21" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A21" s="51"/>
-      <c r="B21" s="51"/>
-      <c r="C21" s="38">
-        <v>1</v>
-      </c>
-      <c r="D21" s="38">
+      <c r="A21" s="49"/>
+      <c r="B21" s="49"/>
+      <c r="C21" s="33">
+        <v>1</v>
+      </c>
+      <c r="D21" s="33">
         <f t="shared" si="0"/>
         <v>2E-3</v>
       </c>
-      <c r="E21" s="38" t="s">
+      <c r="E21" s="33" t="s">
         <v>105</v>
       </c>
-      <c r="F21" s="42" t="s">
+      <c r="F21" s="37" t="s">
         <v>88</v>
       </c>
       <c r="G21" s="5"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="51"/>
-      <c r="B22" s="51"/>
-      <c r="C22" s="38">
-        <v>1</v>
-      </c>
-      <c r="D22" s="38">
+      <c r="A22" s="49"/>
+      <c r="B22" s="49"/>
+      <c r="C22" s="33">
+        <v>1</v>
+      </c>
+      <c r="D22" s="33">
         <f t="shared" si="0"/>
         <v>2E-3</v>
       </c>
-      <c r="E22" s="38" t="s">
+      <c r="E22" s="33" t="s">
         <v>81</v>
       </c>
-      <c r="F22" s="42" t="s">
+      <c r="F22" s="37" t="s">
         <v>106</v>
       </c>
       <c r="G22" s="5"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="51"/>
-      <c r="B23" s="51"/>
-      <c r="C23" s="38">
-        <v>1</v>
-      </c>
-      <c r="D23" s="38">
+      <c r="A23" s="49"/>
+      <c r="B23" s="49"/>
+      <c r="C23" s="33">
+        <v>1</v>
+      </c>
+      <c r="D23" s="33">
         <f t="shared" si="0"/>
         <v>2E-3</v>
       </c>
-      <c r="E23" s="38" t="s">
+      <c r="E23" s="33" t="s">
         <v>107</v>
       </c>
-      <c r="F23" s="42" t="s">
+      <c r="F23" s="37" t="s">
         <v>108</v>
       </c>
       <c r="G23" s="5"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="51"/>
-      <c r="B24" s="51"/>
-      <c r="C24" s="38">
-        <v>1</v>
-      </c>
-      <c r="D24" s="38">
+      <c r="A24" s="49"/>
+      <c r="B24" s="49"/>
+      <c r="C24" s="33">
+        <v>1</v>
+      </c>
+      <c r="D24" s="33">
         <f t="shared" si="0"/>
         <v>2E-3</v>
       </c>
-      <c r="E24" s="38" t="s">
+      <c r="E24" s="33" t="s">
         <v>89</v>
       </c>
-      <c r="F24" s="42" t="s">
+      <c r="F24" s="37" t="s">
         <v>90</v>
       </c>
       <c r="G24" s="5"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="51"/>
-      <c r="B25" s="51"/>
-      <c r="C25" s="38">
+      <c r="A25" s="49"/>
+      <c r="B25" s="49"/>
+      <c r="C25" s="33">
         <v>5</v>
       </c>
-      <c r="D25" s="38">
+      <c r="D25" s="33">
         <f t="shared" si="0"/>
         <v>0.01</v>
       </c>
-      <c r="E25" s="38" t="s">
+      <c r="E25" s="33" t="s">
         <v>93</v>
       </c>
-      <c r="F25" s="42" t="s">
+      <c r="F25" s="37" t="s">
         <v>94</v>
       </c>
       <c r="G25" s="5"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="51"/>
-      <c r="B26" s="51"/>
-      <c r="C26" s="38">
-        <v>1</v>
-      </c>
-      <c r="D26" s="38">
+      <c r="A26" s="49"/>
+      <c r="B26" s="49"/>
+      <c r="C26" s="33">
+        <v>1</v>
+      </c>
+      <c r="D26" s="33">
         <f t="shared" si="0"/>
         <v>2E-3</v>
       </c>
-      <c r="E26" s="38" t="s">
+      <c r="E26" s="33" t="s">
         <v>95</v>
       </c>
-      <c r="F26" s="42" t="s">
+      <c r="F26" s="37" t="s">
         <v>96</v>
       </c>
       <c r="G26" s="5"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="51"/>
-      <c r="B27" s="51"/>
-      <c r="C27" s="38">
+      <c r="A27" s="49"/>
+      <c r="B27" s="49"/>
+      <c r="C27" s="33">
         <v>2</v>
       </c>
-      <c r="D27" s="38">
+      <c r="D27" s="33">
         <f t="shared" si="0"/>
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="E27" s="38" t="s">
+      <c r="E27" s="33" t="s">
         <v>91</v>
       </c>
-      <c r="F27" s="42" t="s">
+      <c r="F27" s="37" t="s">
         <v>92</v>
       </c>
       <c r="G27" s="5"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" s="52"/>
-      <c r="B28" s="52"/>
-      <c r="C28" s="38">
-        <v>1</v>
-      </c>
-      <c r="D28" s="38">
+      <c r="A28" s="50"/>
+      <c r="B28" s="50"/>
+      <c r="C28" s="33">
+        <v>1</v>
+      </c>
+      <c r="D28" s="33">
         <f t="shared" si="0"/>
         <v>2E-3</v>
       </c>
-      <c r="E28" s="38" t="s">
+      <c r="E28" s="33" t="s">
         <v>97</v>
       </c>
-      <c r="F28" s="42" t="s">
+      <c r="F28" s="37" t="s">
         <v>98</v>
       </c>
       <c r="G28" s="5"/>
     </row>
     <row r="29" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A29" s="47" t="s">
+      <c r="A29" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="B29" s="47">
-        <v>1</v>
-      </c>
-      <c r="C29" s="39">
-        <v>1</v>
-      </c>
-      <c r="D29" s="39">
+      <c r="B29" s="51">
+        <v>1</v>
+      </c>
+      <c r="C29" s="34">
+        <v>1</v>
+      </c>
+      <c r="D29" s="34">
         <f t="shared" si="0"/>
         <v>2E-3</v>
       </c>
-      <c r="E29" s="41" t="s">
+      <c r="E29" s="36" t="s">
         <v>109</v>
       </c>
-      <c r="F29" s="41" t="s">
+      <c r="F29" s="36" t="s">
         <v>110</v>
       </c>
       <c r="G29" s="5">
@@ -2404,239 +2447,239 @@
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A30" s="48"/>
-      <c r="B30" s="48"/>
-      <c r="C30" s="39">
-        <v>1</v>
-      </c>
-      <c r="D30" s="39">
+      <c r="A30" s="56"/>
+      <c r="B30" s="56"/>
+      <c r="C30" s="34">
+        <v>1</v>
+      </c>
+      <c r="D30" s="34">
         <f t="shared" si="0"/>
         <v>2E-3</v>
       </c>
-      <c r="E30" s="41" t="s">
+      <c r="E30" s="36" t="s">
         <v>81</v>
       </c>
-      <c r="F30" s="41" t="s">
+      <c r="F30" s="36" t="s">
         <v>111</v>
       </c>
       <c r="G30" s="5"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" s="48"/>
-      <c r="B31" s="48"/>
-      <c r="C31" s="39">
+      <c r="A31" s="56"/>
+      <c r="B31" s="56"/>
+      <c r="C31" s="34">
         <v>5</v>
       </c>
-      <c r="D31" s="39">
+      <c r="D31" s="34">
         <f t="shared" si="0"/>
         <v>0.01</v>
       </c>
-      <c r="E31" s="41" t="s">
+      <c r="E31" s="36" t="s">
         <v>101</v>
       </c>
-      <c r="F31" s="41" t="s">
+      <c r="F31" s="36" t="s">
         <v>112</v>
       </c>
       <c r="G31" s="5"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A32" s="48"/>
-      <c r="B32" s="48"/>
-      <c r="C32" s="39">
+      <c r="A32" s="56"/>
+      <c r="B32" s="56"/>
+      <c r="C32" s="34">
         <v>5</v>
       </c>
-      <c r="D32" s="39">
+      <c r="D32" s="34">
         <f t="shared" si="0"/>
         <v>0.01</v>
       </c>
-      <c r="E32" s="41" t="s">
+      <c r="E32" s="36" t="s">
         <v>85</v>
       </c>
-      <c r="F32" s="41" t="s">
+      <c r="F32" s="36" t="s">
         <v>86</v>
       </c>
       <c r="G32" s="5"/>
     </row>
     <row r="33" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A33" s="48"/>
-      <c r="B33" s="48"/>
-      <c r="C33" s="39">
-        <v>1</v>
-      </c>
-      <c r="D33" s="39">
+      <c r="A33" s="56"/>
+      <c r="B33" s="56"/>
+      <c r="C33" s="34">
+        <v>1</v>
+      </c>
+      <c r="D33" s="34">
         <f t="shared" si="0"/>
         <v>2E-3</v>
       </c>
-      <c r="E33" s="41" t="s">
+      <c r="E33" s="36" t="s">
         <v>105</v>
       </c>
-      <c r="F33" s="41" t="s">
+      <c r="F33" s="36" t="s">
         <v>88</v>
       </c>
       <c r="G33" s="5"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" s="48"/>
-      <c r="B34" s="48"/>
-      <c r="C34" s="39">
-        <v>1</v>
-      </c>
-      <c r="D34" s="39">
+      <c r="A34" s="56"/>
+      <c r="B34" s="56"/>
+      <c r="C34" s="34">
+        <v>1</v>
+      </c>
+      <c r="D34" s="34">
         <f t="shared" ref="D34:D65" si="2">ROUND(C34/480,3)</f>
         <v>2E-3</v>
       </c>
-      <c r="E34" s="41" t="s">
+      <c r="E34" s="36" t="s">
         <v>107</v>
       </c>
-      <c r="F34" s="41" t="s">
+      <c r="F34" s="36" t="s">
         <v>113</v>
       </c>
       <c r="G34" s="5"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A35" s="48"/>
-      <c r="B35" s="48"/>
-      <c r="C35" s="39">
+      <c r="A35" s="56"/>
+      <c r="B35" s="56"/>
+      <c r="C35" s="34">
         <v>5</v>
       </c>
-      <c r="D35" s="39">
+      <c r="D35" s="34">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="E35" s="41" t="s">
+      <c r="E35" s="36" t="s">
         <v>83</v>
       </c>
-      <c r="F35" s="41" t="s">
+      <c r="F35" s="36" t="s">
         <v>114</v>
       </c>
       <c r="G35" s="5"/>
     </row>
     <row r="36" spans="1:7" s="14" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A36" s="48"/>
-      <c r="B36" s="48"/>
-      <c r="C36" s="39">
-        <v>1</v>
-      </c>
-      <c r="D36" s="39">
+      <c r="A36" s="56"/>
+      <c r="B36" s="56"/>
+      <c r="C36" s="34">
+        <v>1</v>
+      </c>
+      <c r="D36" s="34">
         <f t="shared" si="2"/>
         <v>2E-3</v>
       </c>
-      <c r="E36" s="41" t="s">
+      <c r="E36" s="36" t="s">
         <v>115</v>
       </c>
-      <c r="F36" s="41" t="s">
+      <c r="F36" s="36" t="s">
         <v>103</v>
       </c>
       <c r="G36" s="23"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A37" s="48"/>
-      <c r="B37" s="48"/>
-      <c r="C37" s="39">
+      <c r="A37" s="56"/>
+      <c r="B37" s="56"/>
+      <c r="C37" s="34">
         <v>5</v>
       </c>
-      <c r="D37" s="39">
+      <c r="D37" s="34">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="E37" s="41" t="s">
+      <c r="E37" s="36" t="s">
         <v>116</v>
       </c>
-      <c r="F37" s="41" t="s">
+      <c r="F37" s="36" t="s">
         <v>117</v>
       </c>
       <c r="G37" s="5"/>
     </row>
     <row r="38" spans="1:7" s="14" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="48"/>
-      <c r="B38" s="48"/>
-      <c r="C38" s="39">
-        <v>1</v>
-      </c>
-      <c r="D38" s="39">
+      <c r="A38" s="56"/>
+      <c r="B38" s="56"/>
+      <c r="C38" s="34">
+        <v>1</v>
+      </c>
+      <c r="D38" s="34">
         <f t="shared" si="2"/>
         <v>2E-3</v>
       </c>
-      <c r="E38" s="41" t="s">
+      <c r="E38" s="36" t="s">
         <v>91</v>
       </c>
-      <c r="F38" s="41" t="s">
+      <c r="F38" s="36" t="s">
         <v>92</v>
       </c>
       <c r="G38" s="23"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A39" s="48"/>
-      <c r="B39" s="48"/>
-      <c r="C39" s="39">
+      <c r="A39" s="56"/>
+      <c r="B39" s="56"/>
+      <c r="C39" s="34">
         <v>5</v>
       </c>
-      <c r="D39" s="39">
+      <c r="D39" s="34">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="E39" s="41" t="s">
+      <c r="E39" s="36" t="s">
         <v>93</v>
       </c>
-      <c r="F39" s="41" t="s">
+      <c r="F39" s="36" t="s">
         <v>94</v>
       </c>
       <c r="G39" s="5"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A40" s="48"/>
-      <c r="B40" s="48"/>
-      <c r="C40" s="39">
-        <v>1</v>
-      </c>
-      <c r="D40" s="39">
+      <c r="A40" s="56"/>
+      <c r="B40" s="56"/>
+      <c r="C40" s="34">
+        <v>1</v>
+      </c>
+      <c r="D40" s="34">
         <f t="shared" si="2"/>
         <v>2E-3</v>
       </c>
-      <c r="E40" s="41" t="s">
+      <c r="E40" s="36" t="s">
         <v>95</v>
       </c>
-      <c r="F40" s="41" t="s">
+      <c r="F40" s="36" t="s">
         <v>96</v>
       </c>
       <c r="G40" s="5"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A41" s="49"/>
-      <c r="B41" s="49"/>
-      <c r="C41" s="39">
-        <v>1</v>
-      </c>
-      <c r="D41" s="39">
+      <c r="A41" s="52"/>
+      <c r="B41" s="52"/>
+      <c r="C41" s="34">
+        <v>1</v>
+      </c>
+      <c r="D41" s="34">
         <f t="shared" si="2"/>
         <v>2E-3</v>
       </c>
-      <c r="E41" s="39" t="s">
+      <c r="E41" s="34" t="s">
         <v>97</v>
       </c>
-      <c r="F41" s="41" t="s">
+      <c r="F41" s="36" t="s">
         <v>98</v>
       </c>
       <c r="G41" s="5"/>
     </row>
-    <row r="42" spans="1:7" s="53" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="50" t="s">
+    <row r="42" spans="1:7" s="38" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="48" t="s">
         <v>10</v>
       </c>
-      <c r="B42" s="50">
-        <v>1</v>
-      </c>
-      <c r="C42" s="38">
-        <v>1</v>
-      </c>
-      <c r="D42" s="38">
+      <c r="B42" s="48">
+        <v>1</v>
+      </c>
+      <c r="C42" s="33">
+        <v>1</v>
+      </c>
+      <c r="D42" s="33">
         <f t="shared" si="2"/>
         <v>2E-3</v>
       </c>
-      <c r="E42" s="38" t="s">
+      <c r="E42" s="33" t="s">
         <v>118</v>
       </c>
-      <c r="F42" s="42" t="s">
+      <c r="F42" s="37" t="s">
         <v>11</v>
       </c>
       <c r="G42" s="21">
@@ -2644,182 +2687,182 @@
         <v>2.4E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:7" s="53" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="51"/>
-      <c r="B43" s="51"/>
-      <c r="C43" s="38">
-        <v>1</v>
-      </c>
-      <c r="D43" s="38">
+    <row r="43" spans="1:7" s="38" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="49"/>
+      <c r="B43" s="49"/>
+      <c r="C43" s="33">
+        <v>1</v>
+      </c>
+      <c r="D43" s="33">
         <f t="shared" si="2"/>
         <v>2E-3</v>
       </c>
-      <c r="E43" s="38" t="s">
+      <c r="E43" s="33" t="s">
         <v>119</v>
       </c>
-      <c r="F43" s="42"/>
+      <c r="F43" s="37"/>
       <c r="G43" s="21"/>
     </row>
-    <row r="44" spans="1:7" s="53" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="51"/>
-      <c r="B44" s="51"/>
-      <c r="C44" s="38">
+    <row r="44" spans="1:7" s="38" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="49"/>
+      <c r="B44" s="49"/>
+      <c r="C44" s="33">
         <v>5</v>
       </c>
-      <c r="D44" s="38">
+      <c r="D44" s="33">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="E44" s="38" t="s">
+      <c r="E44" s="33" t="s">
         <v>85</v>
       </c>
-      <c r="F44" s="42"/>
+      <c r="F44" s="37"/>
       <c r="G44" s="21"/>
     </row>
-    <row r="45" spans="1:7" s="53" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="52"/>
-      <c r="B45" s="52"/>
-      <c r="C45" s="38">
+    <row r="45" spans="1:7" s="38" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="50"/>
+      <c r="B45" s="50"/>
+      <c r="C45" s="33">
         <v>5</v>
       </c>
-      <c r="D45" s="38">
+      <c r="D45" s="33">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="E45" s="38" t="s">
+      <c r="E45" s="33" t="s">
         <v>93</v>
       </c>
-      <c r="F45" s="42"/>
+      <c r="F45" s="37"/>
       <c r="G45" s="21"/>
     </row>
-    <row r="46" spans="1:7" s="54" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="47" t="s">
+    <row r="46" spans="1:7" s="39" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="51" t="s">
         <v>120</v>
       </c>
-      <c r="B46" s="47">
-        <v>1</v>
-      </c>
-      <c r="C46" s="39">
-        <v>1</v>
-      </c>
-      <c r="D46" s="39">
+      <c r="B46" s="51">
+        <v>1</v>
+      </c>
+      <c r="C46" s="34">
+        <v>1</v>
+      </c>
+      <c r="D46" s="34">
         <f t="shared" si="2"/>
         <v>2E-3</v>
       </c>
-      <c r="E46" s="39" t="s">
+      <c r="E46" s="34" t="s">
         <v>118</v>
       </c>
-      <c r="F46" s="41"/>
+      <c r="F46" s="36"/>
       <c r="G46" s="22">
         <f>SUM(D46:D47)</f>
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="47" spans="1:7" s="54" customFormat="1" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="49"/>
-      <c r="B47" s="49"/>
-      <c r="C47" s="39">
-        <v>1</v>
-      </c>
-      <c r="D47" s="39">
+    <row r="47" spans="1:7" s="39" customFormat="1" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="52"/>
+      <c r="B47" s="52"/>
+      <c r="C47" s="34">
+        <v>1</v>
+      </c>
+      <c r="D47" s="34">
         <f t="shared" si="2"/>
         <v>2E-3</v>
       </c>
-      <c r="E47" s="39" t="s">
+      <c r="E47" s="34" t="s">
         <v>119</v>
       </c>
-      <c r="F47" s="41"/>
+      <c r="F47" s="36"/>
       <c r="G47" s="22"/>
     </row>
-    <row r="48" spans="1:7" s="53" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="50" t="s">
+    <row r="48" spans="1:7" s="38" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="48" t="s">
         <v>121</v>
       </c>
-      <c r="B48" s="50">
-        <v>1</v>
-      </c>
-      <c r="C48" s="38">
-        <v>1</v>
-      </c>
-      <c r="D48" s="38">
+      <c r="B48" s="48">
+        <v>1</v>
+      </c>
+      <c r="C48" s="33">
+        <v>1</v>
+      </c>
+      <c r="D48" s="33">
         <f t="shared" si="2"/>
         <v>2E-3</v>
       </c>
-      <c r="E48" s="38" t="s">
+      <c r="E48" s="33" t="s">
         <v>118</v>
       </c>
-      <c r="F48" s="42"/>
+      <c r="F48" s="37"/>
       <c r="G48" s="21">
         <f>SUM(D48:D51)</f>
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="49" spans="1:7" s="53" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="51"/>
-      <c r="B49" s="51"/>
-      <c r="C49" s="38">
-        <v>1</v>
-      </c>
-      <c r="D49" s="38">
+    <row r="49" spans="1:7" s="38" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="49"/>
+      <c r="B49" s="49"/>
+      <c r="C49" s="33">
+        <v>1</v>
+      </c>
+      <c r="D49" s="33">
         <f t="shared" si="2"/>
         <v>2E-3</v>
       </c>
-      <c r="E49" s="38" t="s">
+      <c r="E49" s="33" t="s">
         <v>119</v>
       </c>
-      <c r="F49" s="42"/>
+      <c r="F49" s="37"/>
       <c r="G49" s="21"/>
     </row>
-    <row r="50" spans="1:7" s="53" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="51"/>
-      <c r="B50" s="51"/>
-      <c r="C50" s="38">
-        <v>1</v>
-      </c>
-      <c r="D50" s="38">
+    <row r="50" spans="1:7" s="38" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="49"/>
+      <c r="B50" s="49"/>
+      <c r="C50" s="33">
+        <v>1</v>
+      </c>
+      <c r="D50" s="33">
         <f t="shared" si="2"/>
         <v>2E-3</v>
       </c>
-      <c r="E50" s="38" t="s">
+      <c r="E50" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="F50" s="42"/>
+      <c r="F50" s="37"/>
       <c r="G50" s="21"/>
     </row>
-    <row r="51" spans="1:7" s="53" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="52"/>
-      <c r="B51" s="52"/>
-      <c r="C51" s="38">
-        <v>1</v>
-      </c>
-      <c r="D51" s="38">
+    <row r="51" spans="1:7" s="38" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="50"/>
+      <c r="B51" s="50"/>
+      <c r="C51" s="33">
+        <v>1</v>
+      </c>
+      <c r="D51" s="33">
         <f t="shared" si="2"/>
         <v>2E-3</v>
       </c>
-      <c r="E51" s="38" t="s">
+      <c r="E51" s="33" t="s">
         <v>123</v>
       </c>
-      <c r="F51" s="42"/>
+      <c r="F51" s="37"/>
       <c r="G51" s="21"/>
     </row>
-    <row r="52" spans="1:7" s="54" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="39" t="s">
+    <row r="52" spans="1:7" s="39" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="B52" s="39">
-        <v>1</v>
-      </c>
-      <c r="C52" s="39">
-        <v>1</v>
-      </c>
-      <c r="D52" s="39">
+      <c r="B52" s="34">
+        <v>1</v>
+      </c>
+      <c r="C52" s="34">
+        <v>1</v>
+      </c>
+      <c r="D52" s="34">
         <f t="shared" si="2"/>
         <v>2E-3</v>
       </c>
-      <c r="E52" s="39" t="s">
+      <c r="E52" s="34" t="s">
         <v>173</v>
       </c>
-      <c r="F52" s="55" t="s">
+      <c r="F52" s="40" t="s">
         <v>9</v>
       </c>
       <c r="G52" s="22">
@@ -2827,24 +2870,24 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="53" spans="1:7" s="53" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="38" t="s">
+    <row r="53" spans="1:7" s="38" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="33" t="s">
         <v>124</v>
       </c>
-      <c r="B53" s="38">
-        <v>1</v>
-      </c>
-      <c r="C53" s="38">
+      <c r="B53" s="33">
+        <v>1</v>
+      </c>
+      <c r="C53" s="33">
         <v>5</v>
       </c>
-      <c r="D53" s="38">
+      <c r="D53" s="33">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="E53" s="38" t="s">
+      <c r="E53" s="33" t="s">
         <v>124</v>
       </c>
-      <c r="F53" s="42" t="s">
+      <c r="F53" s="37" t="s">
         <v>125</v>
       </c>
       <c r="G53" s="21">
@@ -2852,24 +2895,24 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="54" spans="1:7" s="54" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="39" t="s">
+    <row r="54" spans="1:7" s="39" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="34" t="s">
         <v>126</v>
       </c>
-      <c r="B54" s="39">
-        <v>1</v>
-      </c>
-      <c r="C54" s="39">
+      <c r="B54" s="34">
+        <v>1</v>
+      </c>
+      <c r="C54" s="34">
         <v>20</v>
       </c>
-      <c r="D54" s="39">
+      <c r="D54" s="34">
         <f t="shared" si="2"/>
         <v>4.2000000000000003E-2</v>
       </c>
-      <c r="E54" s="39" t="s">
+      <c r="E54" s="34" t="s">
         <v>126</v>
       </c>
-      <c r="F54" s="41" t="s">
+      <c r="F54" s="36" t="s">
         <v>127</v>
       </c>
       <c r="G54" s="22">
@@ -2877,24 +2920,24 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="55" spans="1:7" s="53" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="38" t="s">
+    <row r="55" spans="1:7" s="38" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="33" t="s">
         <v>128</v>
       </c>
-      <c r="B55" s="38">
-        <v>1</v>
-      </c>
-      <c r="C55" s="38">
+      <c r="B55" s="33">
+        <v>1</v>
+      </c>
+      <c r="C55" s="33">
         <v>15</v>
       </c>
-      <c r="D55" s="38">
+      <c r="D55" s="33">
         <f t="shared" si="2"/>
         <v>3.1E-2</v>
       </c>
-      <c r="E55" s="38" t="s">
+      <c r="E55" s="33" t="s">
         <v>174</v>
       </c>
-      <c r="F55" s="42" t="s">
+      <c r="F55" s="37" t="s">
         <v>19</v>
       </c>
       <c r="G55" s="21">
@@ -2902,24 +2945,24 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="56" spans="1:7" s="54" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A56" s="39" t="s">
+    <row r="56" spans="1:7" s="39" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A56" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="B56" s="39">
-        <v>1</v>
-      </c>
-      <c r="C56" s="39">
+      <c r="B56" s="34">
+        <v>1</v>
+      </c>
+      <c r="C56" s="34">
         <v>10</v>
       </c>
-      <c r="D56" s="39">
+      <c r="D56" s="34">
         <f t="shared" si="2"/>
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="E56" s="41" t="s">
+      <c r="E56" s="36" t="s">
         <v>175</v>
       </c>
-      <c r="F56" s="41" t="s">
+      <c r="F56" s="36" t="s">
         <v>129</v>
       </c>
       <c r="G56" s="22">
@@ -2927,24 +2970,24 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="57" spans="1:7" s="53" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A57" s="38" t="s">
+    <row r="57" spans="1:7" s="38" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A57" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="B57" s="38">
-        <v>1</v>
-      </c>
-      <c r="C57" s="38">
+      <c r="B57" s="33">
+        <v>1</v>
+      </c>
+      <c r="C57" s="33">
         <v>5</v>
       </c>
-      <c r="D57" s="38">
+      <c r="D57" s="33">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="E57" s="42" t="s">
+      <c r="E57" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="F57" s="42" t="s">
+      <c r="F57" s="37" t="s">
         <v>14</v>
       </c>
       <c r="G57" s="21">
@@ -2952,22 +2995,22 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="58" spans="1:7" s="54" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="39" t="s">
+    <row r="58" spans="1:7" s="39" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="B58" s="39"/>
-      <c r="C58" s="39">
-        <v>1</v>
-      </c>
-      <c r="D58" s="39">
+      <c r="B58" s="34"/>
+      <c r="C58" s="34">
+        <v>1</v>
+      </c>
+      <c r="D58" s="34">
         <f t="shared" si="2"/>
         <v>2E-3</v>
       </c>
-      <c r="E58" s="39" t="s">
+      <c r="E58" s="34" t="s">
         <v>176</v>
       </c>
-      <c r="F58" s="39" t="s">
+      <c r="F58" s="34" t="s">
         <v>130</v>
       </c>
       <c r="G58" s="22">
@@ -2976,23 +3019,23 @@
       </c>
     </row>
     <row r="59" spans="1:7" ht="72" x14ac:dyDescent="0.3">
-      <c r="A59" s="38" t="s">
+      <c r="A59" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="B59" s="38">
-        <v>1</v>
-      </c>
-      <c r="C59" s="38">
+      <c r="B59" s="33">
+        <v>1</v>
+      </c>
+      <c r="C59" s="33">
         <v>26</v>
       </c>
-      <c r="D59" s="38">
+      <c r="D59" s="33">
         <f t="shared" si="2"/>
         <v>5.3999999999999999E-2</v>
       </c>
-      <c r="E59" s="43" t="s">
+      <c r="E59" s="37" t="s">
         <v>177</v>
       </c>
-      <c r="F59" s="42" t="s">
+      <c r="F59" s="37" t="s">
         <v>131</v>
       </c>
       <c r="G59" s="21">
@@ -3001,23 +3044,23 @@
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A60" s="39" t="s">
+      <c r="A60" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="B60" s="39">
-        <v>1</v>
-      </c>
-      <c r="C60" s="39">
+      <c r="B60" s="34">
+        <v>1</v>
+      </c>
+      <c r="C60" s="34">
         <v>10</v>
       </c>
-      <c r="D60" s="39">
+      <c r="D60" s="34">
         <f t="shared" si="2"/>
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="E60" s="39" t="s">
+      <c r="E60" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="F60" s="39" t="s">
+      <c r="F60" s="34" t="s">
         <v>18</v>
       </c>
       <c r="G60" s="22">
@@ -3026,23 +3069,23 @@
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A61" s="38" t="s">
+      <c r="A61" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="B61" s="38">
-        <v>1</v>
-      </c>
-      <c r="C61" s="38">
+      <c r="B61" s="33">
+        <v>1</v>
+      </c>
+      <c r="C61" s="33">
         <v>10</v>
       </c>
-      <c r="D61" s="38">
+      <c r="D61" s="33">
         <f t="shared" si="2"/>
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="E61" s="38" t="s">
+      <c r="E61" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="F61" s="38" t="s">
+      <c r="F61" s="33" t="s">
         <v>21</v>
       </c>
       <c r="G61" s="21">
@@ -3051,23 +3094,23 @@
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A62" s="39" t="s">
+      <c r="A62" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="B62" s="39">
-        <v>1</v>
-      </c>
-      <c r="C62" s="39">
+      <c r="B62" s="34">
+        <v>1</v>
+      </c>
+      <c r="C62" s="34">
         <v>60</v>
       </c>
-      <c r="D62" s="39">
+      <c r="D62" s="34">
         <f t="shared" si="2"/>
         <v>0.125</v>
       </c>
-      <c r="E62" s="39" t="s">
+      <c r="E62" s="34" t="s">
         <v>178</v>
       </c>
-      <c r="F62" s="39" t="s">
+      <c r="F62" s="34" t="s">
         <v>23</v>
       </c>
       <c r="G62" s="22">
@@ -3076,23 +3119,23 @@
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A63" s="38" t="s">
+      <c r="A63" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="B63" s="38">
-        <v>1</v>
-      </c>
-      <c r="C63" s="38">
+      <c r="B63" s="33">
+        <v>1</v>
+      </c>
+      <c r="C63" s="33">
         <v>5</v>
       </c>
-      <c r="D63" s="38">
+      <c r="D63" s="33">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="E63" s="38" t="s">
+      <c r="E63" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="F63" s="38" t="s">
+      <c r="F63" s="33" t="s">
         <v>25</v>
       </c>
       <c r="G63" s="21">
@@ -3100,24 +3143,24 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="64" spans="1:7" s="54" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A64" s="39" t="s">
+    <row r="64" spans="1:7" s="39" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A64" s="34" t="s">
         <v>132</v>
       </c>
-      <c r="B64" s="39">
-        <v>1</v>
-      </c>
-      <c r="C64" s="39">
+      <c r="B64" s="34">
+        <v>1</v>
+      </c>
+      <c r="C64" s="34">
         <v>10</v>
       </c>
-      <c r="D64" s="39">
+      <c r="D64" s="34">
         <f t="shared" si="2"/>
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="E64" s="41" t="s">
+      <c r="E64" s="36" t="s">
         <v>179</v>
       </c>
-      <c r="F64" s="39" t="s">
+      <c r="F64" s="34" t="s">
         <v>133</v>
       </c>
       <c r="G64" s="22">
@@ -3126,23 +3169,23 @@
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A65" s="38" t="s">
+      <c r="A65" s="33" t="s">
         <v>134</v>
       </c>
-      <c r="B65" s="38">
-        <v>1</v>
-      </c>
-      <c r="C65" s="38">
+      <c r="B65" s="33">
+        <v>1</v>
+      </c>
+      <c r="C65" s="33">
         <v>10</v>
       </c>
-      <c r="D65" s="38">
+      <c r="D65" s="33">
         <f t="shared" si="2"/>
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="E65" s="38" t="s">
+      <c r="E65" s="33" t="s">
         <v>180</v>
       </c>
-      <c r="F65" s="38" t="s">
+      <c r="F65" s="33" t="s">
         <v>135</v>
       </c>
       <c r="G65" s="21">
@@ -3151,23 +3194,23 @@
       </c>
     </row>
     <row r="66" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A66" s="39" t="s">
+      <c r="A66" s="34" t="s">
         <v>136</v>
       </c>
-      <c r="B66" s="39">
-        <v>1</v>
-      </c>
-      <c r="C66" s="39">
+      <c r="B66" s="34">
+        <v>1</v>
+      </c>
+      <c r="C66" s="34">
         <v>5</v>
       </c>
-      <c r="D66" s="39">
+      <c r="D66" s="34">
         <f>ROUNDUP(C66/480,2)</f>
         <v>0.02</v>
       </c>
-      <c r="E66" s="41" t="s">
+      <c r="E66" s="36" t="s">
         <v>181</v>
       </c>
-      <c r="F66" s="39" t="s">
+      <c r="F66" s="34" t="s">
         <v>137</v>
       </c>
       <c r="G66" s="24">
@@ -3176,23 +3219,23 @@
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A67" s="38" t="s">
+      <c r="A67" s="33" t="s">
         <v>138</v>
       </c>
-      <c r="B67" s="38">
-        <v>1</v>
-      </c>
-      <c r="C67" s="38">
+      <c r="B67" s="33">
+        <v>1</v>
+      </c>
+      <c r="C67" s="33">
         <v>5</v>
       </c>
-      <c r="D67" s="38">
+      <c r="D67" s="33">
         <f>ROUNDUP(C67/480,2)</f>
         <v>0.02</v>
       </c>
-      <c r="E67" s="38" t="s">
+      <c r="E67" s="33" t="s">
         <v>182</v>
       </c>
-      <c r="F67" s="38" t="s">
+      <c r="F67" s="33" t="s">
         <v>139</v>
       </c>
       <c r="G67" s="25">
@@ -3313,25 +3356,25 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A3:A15"/>
+    <mergeCell ref="B3:B15"/>
+    <mergeCell ref="A16:A28"/>
+    <mergeCell ref="B16:B28"/>
+    <mergeCell ref="A29:A41"/>
+    <mergeCell ref="B29:B41"/>
     <mergeCell ref="A42:A45"/>
     <mergeCell ref="B42:B45"/>
     <mergeCell ref="A46:A47"/>
     <mergeCell ref="B46:B47"/>
     <mergeCell ref="A48:A51"/>
     <mergeCell ref="B48:B51"/>
-    <mergeCell ref="A3:A15"/>
-    <mergeCell ref="B3:B15"/>
-    <mergeCell ref="A16:A28"/>
-    <mergeCell ref="B16:B28"/>
-    <mergeCell ref="A29:A41"/>
-    <mergeCell ref="B29:B41"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50C86305-C21D-4FA3-98EF-44A7A63E57A3}">
   <dimension ref="A2:E19"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -3630,34 +3673,34 @@
       </c>
     </row>
     <row r="18" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="35">
+      <c r="A18" s="30">
         <v>16</v>
       </c>
-      <c r="B18" s="56" t="s">
+      <c r="B18" s="41" t="s">
         <v>170</v>
       </c>
-      <c r="C18" s="36">
+      <c r="C18" s="31">
         <v>5</v>
       </c>
-      <c r="D18" s="36">
+      <c r="D18" s="31">
         <v>0.02</v>
       </c>
-      <c r="E18" s="36" t="s">
+      <c r="E18" s="31" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="35">
+      <c r="A19" s="30">
         <v>17</v>
       </c>
-      <c r="B19" s="57"/>
-      <c r="C19" s="36">
+      <c r="B19" s="42"/>
+      <c r="C19" s="31">
         <v>20</v>
       </c>
-      <c r="D19" s="36">
+      <c r="D19" s="31">
         <v>0.05</v>
       </c>
-      <c r="E19" s="36" t="s">
+      <c r="E19" s="31" t="s">
         <v>172</v>
       </c>
     </row>
@@ -3669,29 +3712,368 @@
 </worksheet>
 </file>
 
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC7D4B06-F987-4949-B688-FE62E1D2267B}">
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="32.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="57" t="s">
+        <v>140</v>
+      </c>
+      <c r="B1" s="58" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="57" t="s">
+        <v>141</v>
+      </c>
+      <c r="D1" s="57" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="59" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="60">
+        <v>1</v>
+      </c>
+      <c r="B2" s="61" t="s">
+        <v>183</v>
+      </c>
+      <c r="C2" s="61">
+        <v>5</v>
+      </c>
+      <c r="D2" s="61">
+        <v>0.02</v>
+      </c>
+      <c r="E2" s="61"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="60">
+        <v>2</v>
+      </c>
+      <c r="B3" s="62" t="s">
+        <v>184</v>
+      </c>
+      <c r="C3" s="61">
+        <v>5</v>
+      </c>
+      <c r="D3" s="61">
+        <v>0.02</v>
+      </c>
+      <c r="E3" s="61"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="60">
+        <v>3</v>
+      </c>
+      <c r="B4" s="62" t="s">
+        <v>185</v>
+      </c>
+      <c r="C4" s="61">
+        <v>5</v>
+      </c>
+      <c r="D4" s="61">
+        <v>0.02</v>
+      </c>
+      <c r="E4" s="61"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="60">
+        <v>4</v>
+      </c>
+      <c r="B5" s="62" t="s">
+        <v>186</v>
+      </c>
+      <c r="C5" s="61">
+        <v>20</v>
+      </c>
+      <c r="D5" s="61">
+        <v>0.05</v>
+      </c>
+      <c r="E5" s="61"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="60">
+        <v>5</v>
+      </c>
+      <c r="B6" s="62" t="s">
+        <v>187</v>
+      </c>
+      <c r="C6" s="61">
+        <v>5</v>
+      </c>
+      <c r="D6" s="61">
+        <v>0.02</v>
+      </c>
+      <c r="E6" s="61"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="60">
+        <v>6</v>
+      </c>
+      <c r="B7" s="62" t="s">
+        <v>188</v>
+      </c>
+      <c r="C7" s="61">
+        <v>10</v>
+      </c>
+      <c r="D7" s="61">
+        <v>0.03</v>
+      </c>
+      <c r="E7" s="61"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="60">
+        <v>7</v>
+      </c>
+      <c r="B8" s="62" t="s">
+        <v>189</v>
+      </c>
+      <c r="C8" s="61">
+        <v>5</v>
+      </c>
+      <c r="D8" s="61">
+        <v>0.02</v>
+      </c>
+      <c r="E8" s="61"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="60">
+        <v>8</v>
+      </c>
+      <c r="B9" s="61" t="s">
+        <v>190</v>
+      </c>
+      <c r="C9" s="61">
+        <v>5</v>
+      </c>
+      <c r="D9" s="61">
+        <v>0.02</v>
+      </c>
+      <c r="E9" s="61"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="60">
+        <v>9</v>
+      </c>
+      <c r="B10" s="61" t="s">
+        <v>191</v>
+      </c>
+      <c r="C10" s="61">
+        <v>10</v>
+      </c>
+      <c r="D10" s="61">
+        <v>0.03</v>
+      </c>
+      <c r="E10" s="61"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="60">
+        <v>10</v>
+      </c>
+      <c r="B11" s="61" t="s">
+        <v>192</v>
+      </c>
+      <c r="C11" s="61">
+        <v>10</v>
+      </c>
+      <c r="D11" s="61">
+        <v>0.03</v>
+      </c>
+      <c r="E11" s="61"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a70b3f0f-ad95-4873-a867-1db42e3f490d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="5b474486-32f2-4b1b-92da-a10adc11c819" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F21C33C-C8B9-469A-A9B7-0B790C3B831C}">
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="32.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="63" t="s">
+        <v>140</v>
+      </c>
+      <c r="B1" s="64" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="63" t="s">
+        <v>141</v>
+      </c>
+      <c r="D1" s="63" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="65" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="66">
+        <v>1</v>
+      </c>
+      <c r="B2" s="61" t="s">
+        <v>183</v>
+      </c>
+      <c r="C2" s="61">
+        <v>5</v>
+      </c>
+      <c r="D2" s="61">
+        <v>0.02</v>
+      </c>
+      <c r="E2" s="61"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="66">
+        <v>2</v>
+      </c>
+      <c r="B3" s="62" t="s">
+        <v>184</v>
+      </c>
+      <c r="C3" s="61">
+        <v>5</v>
+      </c>
+      <c r="D3" s="61">
+        <v>0.02</v>
+      </c>
+      <c r="E3" s="61"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="66">
+        <v>3</v>
+      </c>
+      <c r="B4" s="62" t="s">
+        <v>185</v>
+      </c>
+      <c r="C4" s="61">
+        <v>5</v>
+      </c>
+      <c r="D4" s="61">
+        <v>0.02</v>
+      </c>
+      <c r="E4" s="61"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="66">
+        <v>4</v>
+      </c>
+      <c r="B5" s="62" t="s">
+        <v>186</v>
+      </c>
+      <c r="C5" s="61">
+        <v>20</v>
+      </c>
+      <c r="D5" s="61">
+        <v>0.05</v>
+      </c>
+      <c r="E5" s="61"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="66">
+        <v>5</v>
+      </c>
+      <c r="B6" s="62" t="s">
+        <v>187</v>
+      </c>
+      <c r="C6" s="61">
+        <v>5</v>
+      </c>
+      <c r="D6" s="61">
+        <v>0.02</v>
+      </c>
+      <c r="E6" s="61"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="66">
+        <v>6</v>
+      </c>
+      <c r="B7" s="62" t="s">
+        <v>188</v>
+      </c>
+      <c r="C7" s="61">
+        <v>30</v>
+      </c>
+      <c r="D7" s="61">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="E7" s="61"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="66">
+        <v>7</v>
+      </c>
+      <c r="B8" s="62" t="s">
+        <v>189</v>
+      </c>
+      <c r="C8" s="61">
+        <v>5</v>
+      </c>
+      <c r="D8" s="61">
+        <v>0.02</v>
+      </c>
+      <c r="E8" s="61"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="66">
+        <v>8</v>
+      </c>
+      <c r="B9" s="61" t="s">
+        <v>193</v>
+      </c>
+      <c r="C9" s="61">
+        <v>10</v>
+      </c>
+      <c r="D9" s="61">
+        <v>0.03</v>
+      </c>
+      <c r="E9" s="61"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="66">
+        <v>9</v>
+      </c>
+      <c r="B10" s="61" t="s">
+        <v>194</v>
+      </c>
+      <c r="C10" s="61">
+        <v>10</v>
+      </c>
+      <c r="D10" s="61">
+        <v>0.03</v>
+      </c>
+      <c r="E10" s="61"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="66">
+        <v>10</v>
+      </c>
+      <c r="B11" s="61" t="s">
+        <v>195</v>
+      </c>
+      <c r="C11" s="61">
+        <v>5</v>
+      </c>
+      <c r="D11" s="61">
+        <v>0.02</v>
+      </c>
+      <c r="E11" s="61"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A235BAA16712F34E858055A6F58A9183" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="154e6db936ca119220ee03b28568bc48">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="a70b3f0f-ad95-4873-a867-1db42e3f490d" xmlns:ns3="5b474486-32f2-4b1b-92da-a10adc11c819" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5d8e43c21c4ad456180d430ee7a121b1" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -3909,10 +4291,44 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a70b3f0f-ad95-4873-a867-1db42e3f490d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="5b474486-32f2-4b1b-92da-a10adc11c819" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0D637D43-A3FC-4B98-B3E7-6C31DD9751AC}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71194988-8BCF-4C00-9CAF-885ACF4ABE4D}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="a70b3f0f-ad95-4873-a867-1db42e3f490d"/>
+    <ds:schemaRef ds:uri="5b474486-32f2-4b1b-92da-a10adc11c819"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -3930,21 +4346,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71194988-8BCF-4C00-9CAF-885ACF4ABE4D}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0D637D43-A3FC-4B98-B3E7-6C31DD9751AC}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="a70b3f0f-ad95-4873-a867-1db42e3f490d"/>
-    <ds:schemaRef ds:uri="5b474486-32f2-4b1b-92da-a10adc11c819"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>